--- a/src/data/downloads/local_2014_2016_oct_sakrebulo_by_election_20161008_data.xlsx
+++ b/src/data/downloads/local_2014_2016_oct_sakrebulo_by_election_20161008_data.xlsx
@@ -554,7 +554,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-21T18:04:35.562Z</t>
+    <t>2026-05-22T15:27:24.647Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_oct_sakrebulo_by_election_20161008_data.xlsx
+++ b/src/data/downloads/local_2014_2016_oct_sakrebulo_by_election_20161008_data.xlsx
@@ -554,7 +554,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-22T15:27:24.647Z</t>
+    <t>2026-05-22T15:52:44.832Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_oct_sakrebulo_by_election_20161008_data.xlsx
+++ b/src/data/downloads/local_2014_2016_oct_sakrebulo_by_election_20161008_data.xlsx
@@ -554,7 +554,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-22T15:52:44.832Z</t>
+    <t>2026-05-24T22:28:17.950Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_oct_sakrebulo_by_election_20161008_data.xlsx
+++ b/src/data/downloads/local_2014_2016_oct_sakrebulo_by_election_20161008_data.xlsx
@@ -554,7 +554,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-24T22:28:17.950Z</t>
+    <t>2026-05-25T13:08:48.807Z</t>
   </si>
   <si>
     <t>Data Source</t>
